--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_precios_e_inflacion.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>78.01074795172229</v>
+        <v>78.01074795172219</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15019,7 +15019,7 @@
         </is>
       </c>
       <c r="N190" s="6" t="n">
-        <v>126.090212316096</v>
+        <v>126.090212316095</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="N192" s="6" t="n">
-        <v>214.694740551494</v>
+        <v>214.694740551493</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>348.167562329311</v>
+        <v>348.16756232931</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20196,7 +20196,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>21.0689956331876</v>
+        <v>21.0689956331875</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20354,7 +20354,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>62.1686499794829</v>
+        <v>62.1686499794828</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23773,7 +23773,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24484,7 +24484,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25037,7 +25037,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31646,7 +31646,7 @@
         </is>
       </c>
       <c r="N403" s="6" t="n">
-        <v>0.00334958333233334</v>
+        <v>0.00334958333233333</v>
       </c>
       <c r="O403" s="4" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31804,7 +31804,7 @@
         </is>
       </c>
       <c r="N405" s="6" t="n">
-        <v>0.00334966666566667</v>
+        <v>0.00334966666566666</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33542,7 +33542,7 @@
         </is>
       </c>
       <c r="N427" s="6" t="n">
-        <v>0.00701666666666667</v>
+        <v>0.00701666666666666</v>
       </c>
       <c r="O427" s="4" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="N432" s="6" t="n">
-        <v>0.0346916666666667</v>
+        <v>0.0346916666666666</v>
       </c>
       <c r="O432" s="4" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34016,7 +34016,7 @@
         </is>
       </c>
       <c r="N433" s="6" t="n">
-        <v>0.0468916666666667</v>
+        <v>0.0468916666666666</v>
       </c>
       <c r="O433" s="4" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34253,7 +34253,7 @@
         </is>
       </c>
       <c r="N436" s="6" t="n">
-        <v>0.0908416666666667</v>
+        <v>0.0908416666666666</v>
       </c>
       <c r="O436" s="4" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34411,7 +34411,7 @@
         </is>
       </c>
       <c r="N438" s="6" t="n">
-        <v>0.176841666666667</v>
+        <v>0.176841666666666</v>
       </c>
       <c r="O438" s="4" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34648,7 +34648,7 @@
         </is>
       </c>
       <c r="N441" s="6" t="n">
-        <v>0.547566666666667</v>
+        <v>0.547566666666666</v>
       </c>
       <c r="O441" s="4" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34806,7 +34806,7 @@
         </is>
       </c>
       <c r="N443" s="6" t="n">
-        <v>0.6799666666666671</v>
+        <v>0.6799666666666661</v>
       </c>
       <c r="O443" s="4" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34885,7 +34885,7 @@
         </is>
       </c>
       <c r="N444" s="6" t="n">
-        <v>0.723658333333334</v>
+        <v>0.723658333333333</v>
       </c>
       <c r="O444" s="4" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35596,7 +35596,7 @@
         </is>
       </c>
       <c r="N453" s="6" t="n">
-        <v>2.58206031746032</v>
+        <v>2.58206031746031</v>
       </c>
       <c r="O453" s="4" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35833,7 +35833,7 @@
         </is>
       </c>
       <c r="N456" s="6" t="n">
-        <v>6.04796184166667</v>
+        <v>6.04796184166666</v>
       </c>
       <c r="O456" s="4" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36070,7 +36070,7 @@
         </is>
       </c>
       <c r="N459" s="6" t="n">
-        <v>9.257344444441671</v>
+        <v>9.25734444444166</v>
       </c>
       <c r="O459" s="4" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36389,7 +36389,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36697,7 +36697,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36774,7 +36774,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36859,7 +36859,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
